--- a/opioid_trends/files for tableau/overdose_deaths_state.xlsx
+++ b/opioid_trends/files for tableau/overdose_deaths_state.xlsx
@@ -7322,10 +7322,10 @@
         <v>45627</v>
       </c>
       <c r="C488" t="n">
-        <v>5149</v>
+        <v>5151</v>
       </c>
       <c r="D488" t="n">
-        <v>24.1286664771613</v>
+        <v>24.1380386529147</v>
       </c>
     </row>
     <row r="489">
@@ -7476,10 +7476,10 @@
         <v>45627</v>
       </c>
       <c r="C499" t="n">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="D499" t="n">
-        <v>28.4457542394176</v>
+        <v>28.4620182498461</v>
       </c>
     </row>
     <row r="500">
@@ -7672,10 +7672,10 @@
         <v>45627</v>
       </c>
       <c r="C513" t="n">
-        <v>4584</v>
+        <v>4585</v>
       </c>
       <c r="D513" t="n">
-        <v>22.7892523618868</v>
+        <v>22.7942238392781</v>
       </c>
     </row>
     <row r="514">
@@ -7824,10 +7824,10 @@
         <v>45627</v>
       </c>
       <c r="C524" t="n">
-        <v>80856</v>
+        <v>80860</v>
       </c>
       <c r="D524" t="n">
-        <v>24.5222176201784</v>
+        <v>24.5234307505643</v>
       </c>
     </row>
     <row r="525">
